--- a/mechanical/the cure BOM RevA 2025-04-15.xlsx
+++ b/mechanical/the cure BOM RevA 2025-04-15.xlsx
@@ -3,15 +3,16 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="575" documentId="13_ncr:1_{6242A4EB-8520-4325-81C8-7EC8ECCF18D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1586AD44-6D51-4685-913E-7150D009BB45}"/>
+  <xr:revisionPtr revIDLastSave="619" documentId="13_ncr:1_{6242A4EB-8520-4325-81C8-7EC8ECCF18D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{007653C8-50E7-4604-A7C0-1F240613D4A1}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="30828" yWindow="36" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="0" yWindow="1536" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="the cure BOM" sheetId="1" r:id="rId1"/>
     <sheet name="revision history" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -677,10 +678,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1181,7 +1178,7 @@
         <v>52</v>
       </c>
       <c r="C9" s="11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>115</v>
@@ -1198,7 +1195,7 @@
       </c>
       <c r="H9" s="12">
         <f t="shared" si="1"/>
-        <v>21.513600000000004</v>
+        <v>28.684800000000003</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
@@ -2069,7 +2066,7 @@
       </c>
       <c r="H44" s="14">
         <f>SUM(H5:H41)</f>
-        <v>391.12796800000001</v>
+        <v>398.29916800000001</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="21" x14ac:dyDescent="0.4">
